--- a/src/test/resources/testdata/testData.xlsx
+++ b/src/test/resources/testdata/testData.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>PRODUCT_NAME</t>
   </si>
@@ -114,10 +114,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -487,16 +499,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="3">
+      <c r="A2" t="s" s="7">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="4">
+      <c r="B2" t="s" s="8">
         <v>5</v>
       </c>
-      <c r="C2" t="s" s="5">
+      <c r="C2" t="s" s="9">
         <v>6</v>
       </c>
-      <c r="D2" t="s" s="6">
+      <c r="D2" t="s" s="10">
         <v>7</v>
       </c>
     </row>

--- a/src/test/resources/testdata/testData.xlsx
+++ b/src/test/resources/testdata/testData.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="8">
   <si>
     <t>PRODUCT_NAME</t>
   </si>
@@ -114,10 +114,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -499,16 +523,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="7">
+      <c r="A2" t="s" s="15">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="8">
+      <c r="B2" t="s" s="16">
         <v>5</v>
       </c>
-      <c r="C2" t="s" s="9">
+      <c r="C2" t="s" s="17">
         <v>6</v>
       </c>
-      <c r="D2" t="s" s="10">
+      <c r="D2" t="s" s="18">
         <v>7</v>
       </c>
     </row>

--- a/src/test/resources/testdata/testData.xlsx
+++ b/src/test/resources/testdata/testData.xlsx
@@ -3,21 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanco\OneDrive\Desktop\ProjectAutomation\Anhtester_CMS_AutomationTestingSeleniumJavaProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735007EE-8902-42A9-A81D-11CE70918ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D7BC02-038A-4DDA-80CB-1DEBE3D4DDF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A2A14C60-8BE7-4BAE-831A-AF93641C5493}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A2A14C60-8BE7-4BAE-831A-AF93641C5493}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Product_list" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
   <si>
     <t>PRODUCT_NAME</t>
   </si>
@@ -56,18 +57,23 @@
     <t>Inhouse product</t>
   </si>
   <si>
-    <t>$1,500.00</t>
-  </si>
-  <si>
     <t>Laptop xịn 2025</t>
+  </si>
+  <si>
+    <t>Giỏ quà Tết attip</t>
+  </si>
+  <si>
+    <t>Giỏ Quà Tết cao cấp, sang trọng dành cho mùa Tết 2024, hứa hẹn sẽ là món quà tinh thần ý nghĩa nhất cho người thân</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +96,19 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -99,7 +118,7 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="1">
@@ -114,57 +133,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -503,9 +492,9 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" customWidth="true" width="29.33203125"/>
-    <col min="4" max="4" customWidth="true" width="17.0"/>
-    <col min="5" max="5" customWidth="true" width="18.77734375"/>
+    <col min="1" max="3" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -522,21 +511,81 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="15">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="16">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s" s="17">
+      <c r="C2" s="4">
+        <v>1500</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" t="s" s="18">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B506733A-0DC9-4FC1-A041-5F31D9FF09D7}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.88671875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" style="6" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="108" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="8">
+        <v>5000000</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1500</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/src/test/resources/testdata/testData.xlsx
+++ b/src/test/resources/testdata/testData.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanco\OneDrive\Desktop\ProjectAutomation\Anhtester_CMS_AutomationTestingSeleniumJavaProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D7BC02-038A-4DDA-80CB-1DEBE3D4DDF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFD03A7-B213-4976-A678-841794033799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A2A14C60-8BE7-4BAE-831A-AF93641C5493}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A2A14C60-8BE7-4BAE-831A-AF93641C5493}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Product_get_list" sheetId="1" r:id="rId1"/>
     <sheet name="Product_list" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -490,14 +490,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204A1FA2-B94E-4C6D-9613-042E9E4E282B}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="29.33203125" customWidth="1"/>
+    <col min="1" max="3" width="29.28515625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="18.77734375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,7 +511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -533,16 +533,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B506733A-0DC9-4FC1-A041-5F31D9FF09D7}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="22.21875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" style="6" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="19.85546875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" style="6" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -556,7 +556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="108" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="131.25" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -570,7 +570,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
